--- a/dtm_dashboard/excel_data/Сводный отчёт Май 2026.xlsx
+++ b/dtm_dashboard/excel_data/Сводный отчёт Май 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\WebstormProjects\dtm\dtm_dashboard\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C092172-4FFC-485E-ACD3-EC5481218545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B82107C9-F5CE-4CA6-86D3-DD47FD16EA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{C17CD275-1CDE-4089-92C8-4CC84D48AF0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{69038B26-F770-4405-98FF-F4821CFE39BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <sheet name="Новосибирск_Пасечная Порошок" sheetId="34" r:id="rId34"/>
     <sheet name="Праздники" sheetId="35" r:id="rId35"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1984,19 +1984,19 @@
     </xf>
   </cellXfs>
   <cellStyles count="13">
-    <cellStyle name="Денежный 2" xfId="5" xr:uid="{E9B11843-BE8F-46DF-8A6D-DD2BFDD17BA2}"/>
-    <cellStyle name="Денежный 2 2" xfId="8" xr:uid="{68397C33-1306-4397-B113-2FE6CBD26AE1}"/>
+    <cellStyle name="Денежный 2" xfId="5" xr:uid="{6258E6BB-0A3C-46B6-8B45-21B577DA7062}"/>
+    <cellStyle name="Денежный 2 2" xfId="8" xr:uid="{9E3C6A53-C011-44E8-90FD-D48A46F9994F}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Обычный 2" xfId="1" xr:uid="{151D1A41-026A-45B8-9F26-DD9B5A2D5843}"/>
-    <cellStyle name="Обычный 5" xfId="6" xr:uid="{60BE4093-6D63-4B25-B629-8D6FCC6C2E2D}"/>
-    <cellStyle name="Обычный 6" xfId="7" xr:uid="{8B55831D-0AD5-41FE-8CE2-71A06DA5BA47}"/>
-    <cellStyle name="Обычный_Биаксплен Новосибирск" xfId="3" xr:uid="{4D92ED94-3A5F-4ADA-A90E-1824C8056673}"/>
-    <cellStyle name="Обычный_Ергарда" xfId="12" xr:uid="{79E71A83-CD84-4BFC-9626-D8C439FC26B5}"/>
-    <cellStyle name="Обычный_Лист1" xfId="10" xr:uid="{6B6D85D6-0E85-4AB1-AB46-CB78B84D3DA1}"/>
-    <cellStyle name="Обычный_РусВинил ББ" xfId="9" xr:uid="{0F2B000F-66C4-445C-9AA2-72C0AFEF0148}"/>
-    <cellStyle name="Обычный_Сибур" xfId="2" xr:uid="{F0247EA9-88C2-41D4-9B88-8600356A2761}"/>
-    <cellStyle name="Обычный_Сибур 1" xfId="4" xr:uid="{6A4A18E5-684B-4257-B00B-75F378F254C9}"/>
-    <cellStyle name="Обычный_СтройТех" xfId="11" xr:uid="{B004E136-11AC-4DAA-B384-36AA27C2FC84}"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{FC8A3FD8-D201-4924-9275-BE015EF49B24}"/>
+    <cellStyle name="Обычный 5" xfId="6" xr:uid="{15442DB9-8DB0-413B-90CE-D88706F067F8}"/>
+    <cellStyle name="Обычный 6" xfId="7" xr:uid="{D949A110-17DD-4CD9-81BB-A24DBF481C21}"/>
+    <cellStyle name="Обычный_Биаксплен Новосибирск" xfId="3" xr:uid="{C6EFFAA2-9CBD-4E12-B26C-3D99DB171B07}"/>
+    <cellStyle name="Обычный_Ергарда" xfId="12" xr:uid="{EB6C9E7C-CB36-467A-9B3F-E5144A750F37}"/>
+    <cellStyle name="Обычный_Лист1" xfId="10" xr:uid="{6BF93FEC-D226-4A36-BB93-1D54D0299CDD}"/>
+    <cellStyle name="Обычный_РусВинил ББ" xfId="9" xr:uid="{D703AE28-BD84-404C-B6E6-9800A4B5CA62}"/>
+    <cellStyle name="Обычный_Сибур" xfId="2" xr:uid="{B42E1B97-27F8-4E72-AB24-36B98A391390}"/>
+    <cellStyle name="Обычный_Сибур 1" xfId="4" xr:uid="{5E7DD9C4-06FA-4421-B3DB-E73709612BA9}"/>
+    <cellStyle name="Обычный_СтройТех" xfId="11" xr:uid="{663A4870-94AE-4599-9561-738A8E47D331}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2327,7 +2327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{169C38AF-A998-42E5-BE65-51D2BCFA8C59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0656D936-EC09-4955-960C-DF438067E9AC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2339,7 +2339,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E155783B-E3FA-43AE-9CD2-2E393F5E6F47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D54CA500-DF5C-4AD8-A1E8-3AE191F5AF77}">
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3459,7 +3459,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32096E72-CFBC-4710-8196-1548394AF8ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E243ABCF-1BC3-48CB-B561-6D98F28CBC03}">
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4524,7 +4524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590FFC5A-EF1C-4443-8412-AF4BF06856E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C905864D-8658-48BB-8C90-851EAEC76FFA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4720,7 +4720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56FEEB72-054C-42C9-8120-CCFAF9214AE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E45381-3F27-4682-854A-88FFC67E356D}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4916,7 +4916,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{246521E7-8A69-450C-862A-B84F32B2FF87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C2AD10-DF4C-4366-804B-4EE6AA9DDCC0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5112,7 +5112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6356FBD9-78EA-49E4-803A-7B5CA5F6D04C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7BBF1E8-C7DC-4AC7-AD88-31751EFC2EC5}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7218,7 +7218,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AED0AF-4DE2-4834-8752-B81FA54F3A04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD6A6AF-B2C9-47B3-8E67-A3D1EDFB3599}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -9324,7 +9324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D88D187-A4B1-4E71-A4A1-6C7288662251}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C711C9-283D-4BDE-8F6E-4FF92A5EA1FC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11430,7 +11430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7CE177-8D28-4D4A-A939-BF555B2CC043}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DB9EC5-E445-4F28-ABE9-0BFE3DE1751B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -13536,7 +13536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B45846E-08D9-45E5-BF4B-807EC574950F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A236266-01C5-42AD-9C08-C5D5B4796694}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -15642,7 +15642,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4F5DAA-330F-4983-8092-276DF0A77AC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8139B923-FB58-4FB8-8CD7-9FF7158A7052}">
   <dimension ref="A1:T40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17735,7 +17735,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B3279E3-9DDA-44A1-A6C4-E318AE821E79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5198EBA5-D58A-43BD-9D55-92764E9DB5CC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -18247,16 +18247,16 @@
         <v>0</v>
       </c>
       <c r="I11" s="62">
-        <v>6.6750000000000007</v>
+        <v>40.948</v>
       </c>
       <c r="J11" s="62">
-        <v>37.625</v>
+        <v>156.62299999999999</v>
       </c>
       <c r="K11" s="63">
-        <v>7.5000000000000011E-2</v>
+        <v>0.69800000000000006</v>
       </c>
       <c r="L11" s="177">
-        <v>11.25</v>
+        <v>104.7</v>
       </c>
       <c r="M11" s="177">
         <v>0</v>
@@ -18274,13 +18274,13 @@
         <v>0</v>
       </c>
       <c r="R11" s="177">
-        <v>6675</v>
+        <v>40948</v>
       </c>
       <c r="S11" s="177">
-        <v>7525</v>
+        <v>31324.6</v>
       </c>
       <c r="T11" s="177">
-        <v>14211.25</v>
+        <v>72377.3</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -18307,16 +18307,16 @@
         <v>0</v>
       </c>
       <c r="I12" s="62">
-        <v>0</v>
+        <v>9.9039999999999999</v>
       </c>
       <c r="J12" s="62">
-        <v>0</v>
+        <v>27.779000000000003</v>
       </c>
       <c r="K12" s="63">
-        <v>0</v>
+        <v>7.2040000000000006</v>
       </c>
       <c r="L12" s="177">
-        <v>0</v>
+        <v>1080.5999999999999</v>
       </c>
       <c r="M12" s="177">
         <v>0</v>
@@ -18334,13 +18334,13 @@
         <v>0</v>
       </c>
       <c r="R12" s="177">
-        <v>0</v>
+        <v>9904</v>
       </c>
       <c r="S12" s="177">
-        <v>0</v>
+        <v>5555.8</v>
       </c>
       <c r="T12" s="177">
-        <v>0</v>
+        <v>16540.400000000001</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -18547,10 +18547,10 @@
         <v>0</v>
       </c>
       <c r="I16" s="62">
-        <v>61.5</v>
+        <v>57</v>
       </c>
       <c r="J16" s="62">
-        <v>61.5</v>
+        <v>57</v>
       </c>
       <c r="K16" s="63">
         <v>0</v>
@@ -18574,13 +18574,13 @@
         <v>0</v>
       </c>
       <c r="R16" s="177">
-        <v>61500</v>
+        <v>57000</v>
       </c>
       <c r="S16" s="177">
-        <v>12300</v>
+        <v>11400</v>
       </c>
       <c r="T16" s="177">
-        <v>73800</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -18967,10 +18967,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="62">
-        <v>5.875</v>
+        <v>0</v>
       </c>
       <c r="J23" s="62">
-        <v>20.299999999999997</v>
+        <v>13.099999999999998</v>
       </c>
       <c r="K23" s="63">
         <v>0</v>
@@ -18994,13 +18994,13 @@
         <v>0</v>
       </c>
       <c r="R23" s="177">
-        <v>5875</v>
+        <v>0</v>
       </c>
       <c r="S23" s="177">
-        <v>4060</v>
+        <v>2620</v>
       </c>
       <c r="T23" s="177">
-        <v>9935</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -19150,7 +19150,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="62">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="63">
         <v>0</v>
@@ -19177,10 +19177,10 @@
         <v>0</v>
       </c>
       <c r="S26" s="177">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T26" s="177">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -19267,16 +19267,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="62">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="J28" s="62">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="K28" s="63">
-        <v>1.375</v>
+        <v>0</v>
       </c>
       <c r="L28" s="177">
-        <v>206.25</v>
+        <v>0</v>
       </c>
       <c r="M28" s="177">
         <v>0</v>
@@ -19294,13 +19294,13 @@
         <v>0</v>
       </c>
       <c r="R28" s="177">
-        <v>2750</v>
+        <v>0</v>
       </c>
       <c r="S28" s="177">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="T28" s="177">
-        <v>4606.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -19327,16 +19327,16 @@
         <v>0</v>
       </c>
       <c r="I29" s="62">
-        <v>2.681</v>
+        <v>0</v>
       </c>
       <c r="J29" s="62">
-        <v>3.1059999999999999</v>
+        <v>0</v>
       </c>
       <c r="K29" s="63">
-        <v>1.2809999999999999</v>
+        <v>0</v>
       </c>
       <c r="L29" s="177">
-        <v>192.15</v>
+        <v>0</v>
       </c>
       <c r="M29" s="177">
         <v>0</v>
@@ -19354,13 +19354,13 @@
         <v>0</v>
       </c>
       <c r="R29" s="177">
-        <v>2681</v>
+        <v>0</v>
       </c>
       <c r="S29" s="177">
-        <v>621.20000000000005</v>
+        <v>0</v>
       </c>
       <c r="T29" s="177">
-        <v>3494.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="I30" s="62">
-        <v>4.1160000000000005</v>
+        <v>0</v>
       </c>
       <c r="J30" s="62">
-        <v>4.1160000000000005</v>
+        <v>0</v>
       </c>
       <c r="K30" s="63">
-        <v>4.1160000000000005</v>
+        <v>0</v>
       </c>
       <c r="L30" s="177">
-        <v>617.4</v>
+        <v>0</v>
       </c>
       <c r="M30" s="177">
         <v>0</v>
@@ -19414,13 +19414,13 @@
         <v>0</v>
       </c>
       <c r="R30" s="177">
-        <v>4116</v>
+        <v>0</v>
       </c>
       <c r="S30" s="177">
-        <v>823.2</v>
+        <v>0</v>
       </c>
       <c r="T30" s="177">
-        <v>5556.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -19507,16 +19507,16 @@
         <v>0</v>
       </c>
       <c r="I32" s="62">
-        <v>32.075999999999993</v>
+        <v>0</v>
       </c>
       <c r="J32" s="62">
-        <v>32.075999999999993</v>
+        <v>0</v>
       </c>
       <c r="K32" s="63">
-        <v>32.075999999999993</v>
+        <v>0</v>
       </c>
       <c r="L32" s="177">
-        <v>4811.3999999999996</v>
+        <v>0</v>
       </c>
       <c r="M32" s="177">
         <v>0</v>
@@ -19534,13 +19534,13 @@
         <v>0</v>
       </c>
       <c r="R32" s="177">
-        <v>32076</v>
+        <v>0</v>
       </c>
       <c r="S32" s="177">
-        <v>6415.2</v>
+        <v>0</v>
       </c>
       <c r="T32" s="177">
-        <v>43302.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -19567,16 +19567,16 @@
         <v>0</v>
       </c>
       <c r="I33" s="62">
-        <v>21.114000000000004</v>
+        <v>0</v>
       </c>
       <c r="J33" s="62">
-        <v>21.114000000000004</v>
+        <v>0</v>
       </c>
       <c r="K33" s="63">
-        <v>21.114000000000004</v>
+        <v>0</v>
       </c>
       <c r="L33" s="177">
-        <v>3167.1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="177">
         <v>0</v>
@@ -19594,13 +19594,13 @@
         <v>0</v>
       </c>
       <c r="R33" s="177">
-        <v>21114</v>
+        <v>0</v>
       </c>
       <c r="S33" s="177">
-        <v>4222.8</v>
+        <v>0</v>
       </c>
       <c r="T33" s="177">
-        <v>28503.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -19627,16 +19627,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="62">
-        <v>7.2919999999999998</v>
+        <v>0</v>
       </c>
       <c r="J34" s="62">
-        <v>8.2669999999999995</v>
+        <v>0</v>
       </c>
       <c r="K34" s="63">
-        <v>6.4169999999999998</v>
+        <v>0</v>
       </c>
       <c r="L34" s="177">
-        <v>962.55</v>
+        <v>0</v>
       </c>
       <c r="M34" s="177">
         <v>0</v>
@@ -19654,13 +19654,13 @@
         <v>0</v>
       </c>
       <c r="R34" s="177">
-        <v>7292</v>
+        <v>0</v>
       </c>
       <c r="S34" s="177">
-        <v>1653.4</v>
+        <v>0</v>
       </c>
       <c r="T34" s="177">
-        <v>9907.9500000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -19740,16 +19740,16 @@
         <v>0</v>
       </c>
       <c r="I36" s="70">
-        <v>339.95599999999996</v>
+        <v>303.72899999999998</v>
       </c>
       <c r="J36" s="70">
-        <v>610.90600000000006</v>
+        <v>669.029</v>
       </c>
       <c r="K36" s="70">
-        <v>78.109000000000009</v>
+        <v>19.557000000000002</v>
       </c>
       <c r="L36" s="178">
-        <v>11716.35</v>
+        <v>2933.55</v>
       </c>
       <c r="M36" s="178">
         <v>830630.95</v>
@@ -19767,20 +19767,20 @@
         <v>0</v>
       </c>
       <c r="R36" s="178">
-        <v>339956</v>
+        <v>303729</v>
       </c>
       <c r="S36" s="178">
-        <v>122181.2</v>
+        <v>133805.79999999999</v>
       </c>
       <c r="T36" s="178">
-        <v>8920458.9299999997</v>
+        <v>8887073.7300000004</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="R37" s="73"/>
       <c r="S37" s="73"/>
       <c r="T37" s="179">
-        <v>10882959.890000001</v>
+        <v>10842229.949999999</v>
       </c>
     </row>
   </sheetData>
@@ -19842,7 +19842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880926CA-B99C-449F-B526-E699AAD88A2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32F97BF-D6CE-465D-A471-6257C31D58D8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -21948,7 +21948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C348E95-54BC-4C38-9DEE-A16EDEECD30B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAB9C4E-3F72-44DF-9D0B-8B855BB701E1}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -24054,7 +24054,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E567F7-2B02-47DF-AEB4-DC8F301EC282}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0090FA5-7E36-4197-9A47-BD6B2E73170B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26160,7 +26160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF2F454-C6D1-4C10-9D48-C66BB80829FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2475746-92D3-4BD9-969D-4E3CDB57E040}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -28264,7 +28264,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EA89575-6ED4-459C-BC5B-2F9F6028C0EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DA71BE-12BE-46DA-BE37-DCC6F457277E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -30368,7 +30368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DDB309E-70D5-4651-B4F9-777A0FCA2CFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877EE4A3-4991-4D9B-AC5B-659464C960B4}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -31050,7 +31050,7 @@
         <v>44.5</v>
       </c>
       <c r="F14" s="180">
-        <v>7389.5259999999998</v>
+        <v>7389.5249999999996</v>
       </c>
       <c r="G14" s="176">
         <v>0</v>
@@ -31110,7 +31110,7 @@
         <v>44</v>
       </c>
       <c r="F15" s="180">
-        <v>7543.5259999999998</v>
+        <v>7543.5249999999996</v>
       </c>
       <c r="G15" s="176">
         <v>0</v>
@@ -31170,7 +31170,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="180">
-        <v>7719.5259999999998</v>
+        <v>7719.5249999999996</v>
       </c>
       <c r="G16" s="176">
         <v>0</v>
@@ -31230,7 +31230,7 @@
         <v>22</v>
       </c>
       <c r="F17" s="180">
-        <v>7829.5259999999998</v>
+        <v>7829.5249999999996</v>
       </c>
       <c r="G17" s="176">
         <v>0</v>
@@ -31290,7 +31290,7 @@
         <v>22.5</v>
       </c>
       <c r="F18" s="180">
-        <v>7873.0259999999998</v>
+        <v>7873.0249999999996</v>
       </c>
       <c r="G18" s="176">
         <v>0</v>
@@ -31350,7 +31350,7 @@
         <v>66</v>
       </c>
       <c r="F19" s="180">
-        <v>7807.0259999999998</v>
+        <v>7807.0249999999996</v>
       </c>
       <c r="G19" s="176">
         <v>0</v>
@@ -31410,7 +31410,7 @@
         <v>264</v>
       </c>
       <c r="F20" s="180">
-        <v>7543.0259999999998</v>
+        <v>7543.0249999999996</v>
       </c>
       <c r="G20" s="176">
         <v>0</v>
@@ -31470,7 +31470,7 @@
         <v>89</v>
       </c>
       <c r="F21" s="180">
-        <v>7454.0259999999998</v>
+        <v>7454.0249999999996</v>
       </c>
       <c r="G21" s="176">
         <v>0</v>
@@ -31530,7 +31530,7 @@
         <v>110</v>
       </c>
       <c r="F22" s="180">
-        <v>7344.0259999999998</v>
+        <v>7344.0249999999996</v>
       </c>
       <c r="G22" s="176">
         <v>0</v>
@@ -31590,7 +31590,7 @@
         <v>44</v>
       </c>
       <c r="F23" s="180">
-        <v>7322.5259999999998</v>
+        <v>7322.5249999999996</v>
       </c>
       <c r="G23" s="176">
         <v>0</v>
@@ -31650,7 +31650,7 @@
         <v>44</v>
       </c>
       <c r="F24" s="180">
-        <v>7368.0259999999998</v>
+        <v>7368.0249999999996</v>
       </c>
       <c r="G24" s="176">
         <v>0</v>
@@ -31710,7 +31710,7 @@
         <v>198</v>
       </c>
       <c r="F25" s="180">
-        <v>7370.5259999999998</v>
+        <v>7370.5249999999996</v>
       </c>
       <c r="G25" s="176">
         <v>0</v>
@@ -31770,7 +31770,7 @@
         <v>88</v>
       </c>
       <c r="F26" s="180">
-        <v>7437.0259999999998</v>
+        <v>7437.0249999999996</v>
       </c>
       <c r="G26" s="176">
         <v>0</v>
@@ -31830,7 +31830,7 @@
         <v>122.375</v>
       </c>
       <c r="F27" s="180">
-        <v>7402.6509999999998</v>
+        <v>7402.65</v>
       </c>
       <c r="G27" s="176">
         <v>0</v>
@@ -31890,7 +31890,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="180">
-        <v>7490.6509999999998</v>
+        <v>7490.65</v>
       </c>
       <c r="G28" s="176">
         <v>0</v>
@@ -31950,7 +31950,7 @@
         <v>88</v>
       </c>
       <c r="F29" s="180">
-        <v>7446.6509999999998</v>
+        <v>7446.65</v>
       </c>
       <c r="G29" s="176">
         <v>0</v>
@@ -32010,7 +32010,7 @@
         <v>22</v>
       </c>
       <c r="F30" s="180">
-        <v>7447.1509999999998</v>
+        <v>7447.15</v>
       </c>
       <c r="G30" s="176">
         <v>0</v>
@@ -32070,7 +32070,7 @@
         <v>352</v>
       </c>
       <c r="F31" s="180">
-        <v>7272.6509999999998</v>
+        <v>7272.65</v>
       </c>
       <c r="G31" s="176">
         <v>0</v>
@@ -32130,7 +32130,7 @@
         <v>110</v>
       </c>
       <c r="F32" s="180">
-        <v>7250.6509999999998</v>
+        <v>7250.65</v>
       </c>
       <c r="G32" s="176">
         <v>0</v>
@@ -32190,7 +32190,7 @@
         <v>154</v>
       </c>
       <c r="F33" s="180">
-        <v>7250.6509999999998</v>
+        <v>7250.65</v>
       </c>
       <c r="G33" s="176">
         <v>0</v>
@@ -32250,7 +32250,7 @@
         <v>157.375</v>
       </c>
       <c r="F34" s="180">
-        <v>7357.2759999999998</v>
+        <v>7357.2749999999996</v>
       </c>
       <c r="G34" s="176">
         <v>0</v>
@@ -32310,7 +32310,7 @@
         <v>174.75</v>
       </c>
       <c r="F35" s="180">
-        <v>7314.5259999999998</v>
+        <v>7314.5249999999996</v>
       </c>
       <c r="G35" s="176">
         <v>0</v>
@@ -32363,7 +32363,7 @@
         <v>2895.5</v>
       </c>
       <c r="F36" s="70">
-        <v>228113.42200000017</v>
+        <v>228113.39999999988</v>
       </c>
       <c r="G36" s="70">
         <v>0</v>
@@ -32393,7 +32393,7 @@
         <v>5107200</v>
       </c>
       <c r="P36" s="178">
-        <v>1279975.82</v>
+        <v>1279975.2</v>
       </c>
       <c r="Q36" s="178">
         <v>0</v>
@@ -32405,14 +32405,14 @@
         <v>0</v>
       </c>
       <c r="T36" s="178">
-        <v>7809895.8200000003</v>
+        <v>7809895.2000000002</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="R37" s="73"/>
       <c r="S37" s="73"/>
       <c r="T37" s="179">
-        <v>9528072.9000000004</v>
+        <v>9528072.1400000006</v>
       </c>
     </row>
   </sheetData>
@@ -32474,7 +32474,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7157783-B504-458D-829A-55EF8BEC4E45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7A470C-1551-4FCC-AA12-2A8CF19D51B5}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -34580,7 +34580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E90F602-1C32-42DB-B9B4-54A5B6FDD692}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52295A38-C9BB-415B-891C-DE38BD15189E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -36686,7 +36686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9402BC6F-7929-423E-817D-A57D0BBA86A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F169944A-CD95-4184-B41E-F694D792FD7B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -38792,7 +38792,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EB4EB26-D414-4C9D-950E-9814E7ECB292}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D7D4530-C8F0-4935-93A9-AC7AE84FDD5A}">
   <dimension ref="A1:M125"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -38813,7 +38813,7 @@
     <row r="1" spans="1:10" ht="161.25" customHeight="1" thickBot="1">
       <c r="A1" s="183">
         <f ca="1">G16</f>
-        <v>129244044.34736</v>
+        <v>131327943.64735998</v>
       </c>
       <c r="B1" s="116"/>
       <c r="C1" s="116"/>
@@ -38937,7 +38937,7 @@
       </c>
       <c r="B6" s="87">
         <f t="shared" ca="1" si="0"/>
-        <v>12268824.52</v>
+        <v>12228094.579999998</v>
       </c>
       <c r="C6" s="87">
         <v>0</v>
@@ -38956,7 +38956,7 @@
       </c>
       <c r="G6" s="88">
         <f t="shared" ca="1" si="4"/>
-        <v>12268824.52</v>
+        <v>12228094.579999998</v>
       </c>
       <c r="I6" s="89" t="s">
         <v>31</v>
@@ -39069,7 +39069,7 @@
       </c>
       <c r="B10" s="87">
         <f t="shared" ca="1" si="0"/>
-        <v>9559792.9000000004</v>
+        <v>9559792.1400000006</v>
       </c>
       <c r="C10" s="87">
         <v>0</v>
@@ -39088,7 +39088,7 @@
       </c>
       <c r="G10" s="88">
         <f t="shared" ca="1" si="4"/>
-        <v>9559792.9000000004</v>
+        <v>9559792.1400000006</v>
       </c>
       <c r="I10" s="89" t="s">
         <v>35</v>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="C13" s="87">
         <f ca="1">C29+C37</f>
-        <v>49822732</v>
+        <v>51947362</v>
       </c>
       <c r="D13" s="87">
         <f t="shared" ca="1" si="1"/>
@@ -39190,7 +39190,7 @@
       </c>
       <c r="G13" s="88">
         <f t="shared" ca="1" si="4"/>
-        <v>49822732</v>
+        <v>51947362</v>
       </c>
       <c r="I13" s="89" t="s">
         <v>37</v>
@@ -39264,11 +39264,11 @@
       <c r="A16" s="3"/>
       <c r="B16" s="93">
         <f t="shared" ref="B16:G16" ca="1" si="5">SUM(B4:B15)</f>
-        <v>79189419.280000001</v>
+        <v>79148688.579999998</v>
       </c>
       <c r="C16" s="93">
         <f t="shared" ca="1" si="5"/>
-        <v>49822732</v>
+        <v>51947362</v>
       </c>
       <c r="D16" s="93">
         <f t="shared" ca="1" si="5"/>
@@ -39284,7 +39284,7 @@
       </c>
       <c r="G16" s="119">
         <f t="shared" ca="1" si="5"/>
-        <v>129244044.34736</v>
+        <v>131327943.64735998</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" thickBot="1">
@@ -39553,7 +39553,7 @@
       <c r="B29" s="96"/>
       <c r="C29" s="97">
         <f ca="1">SUM(C30:C35)</f>
-        <v>39955133</v>
+        <v>42079763</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>48</v>
@@ -39663,7 +39663,7 @@
       <c r="B34" s="16"/>
       <c r="C34" s="8" cm="1">
         <f t="array" aca="1" ref="C34" ca="1">INDIRECT("'" &amp; A29 &amp; "'!F20")</f>
-        <v>17003203</v>
+        <v>19127833</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>44</v>
@@ -39832,7 +39832,7 @@
       <c r="J43" s="103"/>
       <c r="K43" s="104">
         <f ca="1">SUM(M45:M54)</f>
-        <v>79189419.280000001</v>
+        <v>79148688.579999998</v>
       </c>
       <c r="L43" s="105"/>
       <c r="M43" s="106"/>
@@ -39996,7 +39996,7 @@
       </c>
       <c r="D47" s="111" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">IFERROR(INDIRECT("'" &amp; $A47 &amp; " " &amp; D$44 &amp; "'!T37"),)</f>
-        <v>10882959.890000001</v>
+        <v>10842229.949999999</v>
       </c>
       <c r="E47" s="111" cm="1">
         <f t="array" aca="1" ref="E47" ca="1">IFERROR(INDIRECT("'" &amp; $A47 &amp; " " &amp; E$44 &amp; "'!T37"),)</f>
@@ -40032,7 +40032,7 @@
       </c>
       <c r="M47" s="112">
         <f t="shared" ca="1" si="6"/>
-        <v>12268824.52</v>
+        <v>12228094.579999998</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="14.25" customHeight="1">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="D51" s="111" cm="1">
         <f t="array" aca="1" ref="D51" ca="1">IFERROR(INDIRECT("'" &amp; $A51 &amp; " " &amp; D$44 &amp; "'!T37"),)</f>
-        <v>9528072.9000000004</v>
+        <v>9528072.1400000006</v>
       </c>
       <c r="E51" s="111" cm="1">
         <f t="array" aca="1" ref="E51" ca="1">IFERROR(INDIRECT("'" &amp; $A51 &amp; " " &amp; E$44 &amp; "'!T37"),)</f>
@@ -40244,7 +40244,7 @@
       </c>
       <c r="M51" s="112">
         <f t="shared" ca="1" si="6"/>
-        <v>9559792.9000000004</v>
+        <v>9559792.1400000006</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="14.25" customHeight="1">
@@ -40620,7 +40620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68DAA906-7076-43A2-8253-73430B0E12B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B498E5D0-17BB-48FC-966B-6770AA1D98A2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -42726,7 +42726,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEBE1078-8B8E-4D35-90C0-78ACF8ED2EC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1CC8816-420E-4941-AF03-4B94DC2B28E9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -44832,7 +44832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FABD51A-79D2-43AB-9112-0C9ABD91BA33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCFBE32-E742-4FBD-A4FC-FA0686FA1A7C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -46938,7 +46938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BB9FC9-020F-4261-B440-274A61AAC6D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C47AA39F-E8E0-4D3F-8DF0-A6FE9CE44333}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -48989,7 +48989,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18597D52-C17B-41CC-85FC-2C4498F4E5D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC9F53E-BD25-46AE-A200-2E7D649154A1}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -51032,7 +51032,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D980033-409D-4D97-8577-01837D22AD5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797BC852-A4A6-44EF-98B5-8BA37054BAE8}">
   <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -51136,7 +51136,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14CE087D-0C91-4772-8804-2060C5238A0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC9DEF4-3646-4987-ABF0-0C8DED1789BC}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -51180,7 +51180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC59353-45B6-461B-8698-3E3410659DD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0BC8A-AFA2-40D6-AB8B-371AAE2B12CB}">
   <dimension ref="A3:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -51326,8 +51326,8 @@
         <v>61</v>
       </c>
       <c r="F20" s="132">
-        <f>17003203</f>
-        <v>17003203</v>
+        <f>17003203+2124630</f>
+        <v>19127833</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -51364,7 +51364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0054E947-4E48-4988-A39B-3D70E72A8B33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AAA3797-7387-413A-AB79-E6E5F1999A9C}">
   <dimension ref="A1:C137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -51802,7 +51802,7 @@
       </c>
       <c r="C36" s="133">
         <f ca="1">INDEX(INDIRECT("ИТОГО!$B$45:$L$54"),MATCH(Сводка!B36,INDIRECT("ИТОГО!$A$45:$A$54"),0),MATCH(Сводка!A36,INDIRECT("ИТОГО!$B$44:$L$44"),0))</f>
-        <v>10882959.890000001</v>
+        <v>10842229.949999999</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -52462,7 +52462,7 @@
       </c>
       <c r="C91" s="133">
         <f ca="1">INDEX(INDIRECT("ИТОГО!$B$45:$L$54"),MATCH(Сводка!B91,INDIRECT("ИТОГО!$A$45:$A$54"),0),MATCH(Сводка!A91,INDIRECT("ИТОГО!$B$44:$L$44"),0))</f>
-        <v>9528072.9000000004</v>
+        <v>9528072.1400000006</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -52654,7 +52654,7 @@
       </c>
       <c r="C107" s="133" cm="1">
         <f t="array" aca="1" ref="C107" ca="1">INDIRECT("ИТОГО!C34")</f>
-        <v>17003203</v>
+        <v>19127833</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -53023,7 +53023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782C8CE8-04E7-4CF4-B0CA-15DAC0680EA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7246D9EA-5FEA-4FC8-8F1C-12C67E0A8CF6}">
   <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -54822,7 +54822,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BB551D-A752-496D-B8FA-722A48AFE30C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93873FBF-3C22-4125-B117-85B48AD8D0DA}">
   <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -56577,7 +56577,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F340400-F8F4-4C7D-9CCA-EA0D1D449DE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E2CF78-BC36-4A40-A928-87700B58A04C}">
   <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
